--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11091,8 +11091,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -13656,7 +13656,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -7282,13 +7282,13 @@
         <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -8646,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="U95" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V95" s="10" t="n">
         <v>4</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11770,8 +11770,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -13062,7 +13062,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13227,7 +13227,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1391,8 +1391,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2343,8 +2343,8 @@
       <c r="S17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2549,8 +2549,8 @@
       <c r="W19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X19" s="9" t="n">
-        <v>3</v>
+      <c r="X19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -3253,11 +3253,11 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6584</v>
+        <v>3418</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>B. L. T. Toastmasters Club</t>
+          <t>Big Country Toastmasters Club</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3320,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3350,15 +3350,15 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3418</v>
+        <v>6584</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Big Country Toastmasters Club</t>
+          <t>BLT Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3417,19 +3417,19 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6338,8 +6338,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6700,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7690,8 +7690,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>3</v>
+      <c r="X72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8375,8 +8375,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8957,8 +8957,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9904,7 +9904,7 @@
         <v>2</v>
       </c>
       <c r="R95" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S95" s="9" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10121,8 +10121,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="10" t="n">
         <v>2</v>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11188,8 +11188,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11555,8 +11555,8 @@
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="9" t="n">
-        <v>1</v>
+      <c r="S112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12255,8 +12255,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="X123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" s="10" t="n">
         <v>1</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12810,8 +12810,8 @@
       <c r="P125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" s="9" t="n">
-        <v>1</v>
+      <c r="Q125" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13095,7 +13095,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13128,7 +13128,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13227,7 +13227,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13359,7 +13359,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13392,7 +13392,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13656,7 +13656,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13821,7 +13821,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1179,14 +1179,14 @@
       <c r="S5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="9" t="n">
-        <v>0</v>
+      <c r="T5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1476,8 +1476,8 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>0</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,17 +1529,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2058,8 +2058,8 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>0</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2640,8 +2640,8 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>1</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,17 +3178,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3216,8 +3216,8 @@
       <c r="S26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="9" t="n">
-        <v>0</v>
+      <c r="T26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3319,8 +3319,8 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>1</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
@@ -3610,8 +3610,8 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>2</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,17 +4633,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4871,8 +4871,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>2</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,17 +5021,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5059,8 +5059,8 @@
       <c r="S45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
+      <c r="T45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,17 +8125,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8648,14 +8648,14 @@
       <c r="S82" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
+      <c r="T82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>3</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9042,11 +9042,11 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>1</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>4</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9327,8 +9327,8 @@
       <c r="S89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9913,13 +9913,13 @@
         <v>1</v>
       </c>
       <c r="U95" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V95" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10491,8 +10491,8 @@
       <c r="S101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="S102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" s="10" t="n">
         <v>1</v>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10773,8 +10773,8 @@
       <c r="P104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" s="9" t="n">
-        <v>1</v>
+      <c r="Q104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11467,8 +11467,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12137,8 +12137,8 @@
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="9" t="n">
-        <v>1</v>
+      <c r="S118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12340,11 +12340,11 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>0</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>5</v>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -12490,17 +12490,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12625,8 +12625,8 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13077,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13095,7 +13095,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13110,7 +13110,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13128,7 +13128,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -13161,7 +13161,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13194,7 +13194,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13209,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -13242,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -13275,7 +13275,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -13293,7 +13293,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13308,7 +13308,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13341,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13440,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13506,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13539,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13557,7 +13557,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13689,7 +13689,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13770,7 +13770,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -13821,7 +13821,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -13836,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -13854,7 +13854,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1573,8 +1573,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>3</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>4</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" s="9" t="n">
         <v>2</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>4</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -9997,8 +9997,8 @@
       <c r="P96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" s="9" t="n">
-        <v>1</v>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10382,8 +10382,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11364,8 +11364,8 @@
       <c r="S110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="9" t="n">
-        <v>0</v>
+      <c r="T110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T117" s="9" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12437,8 +12437,8 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>3</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13656,7 +13656,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13689,7 +13689,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13821,7 +13821,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -13836,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">

--- a/docs/d/210/inyear.xlsx
+++ b/docs/d/210/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>4</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>2</v>
@@ -2238,7 +2238,7 @@
         <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>6</v>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4677,8 +4677,8 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>1</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5162,8 +5162,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5450,8 +5450,8 @@
       <c r="T49" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
+      <c r="U49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V49" s="9" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5538,8 +5538,8 @@
       <c r="Q50" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R50" s="9" t="n">
-        <v>1</v>
+      <c r="R50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S50" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6902,8 +6902,8 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7002,8 +7002,8 @@
       <c r="T65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
+      <c r="U65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>2</v>
       </c>
       <c r="R95" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S95" s="9" t="n">
         <v>1</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="10" t="n">
         <v>2</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10885,8 +10885,8 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>3</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" s="9" t="n">
         <v>3</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -13260,7 +13260,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13308,7 +13308,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -13326,13 +13326,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13458,7 +13458,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
